--- a/recruiter_forms/028_employee_appraisal_form--recruiter_forms.xlsx
+++ b/recruiter_forms/028_employee_appraisal_form--recruiter_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>employee_rating</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -768,23 +768,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>employee_name_2</t>
+          <t>employee_progress_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Employee Name</t>
+          <t>Employee Progress 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>comments_2</t>
+          <t>areas_for_improvement_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Areas For Improvement 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,276 +814,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>date_2</t>
+          <t>recommended_training_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Recommended Training 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>rating_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Rating</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>comments_3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>date_3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>recommended_training_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Recommended Training</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>areas_for_imprvement_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Areas for Improvement</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>employee_signature_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Employee Signature</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>reviewer_signature_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Reviewer Signature</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>date_of_signature_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Date of Signature</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>date_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>employee_progress_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Employee Progress</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>areas_for_improvement_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Areas for Improvement</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,51 +873,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>employee_rating_choices</t>
+          <t>rating_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>employee_rating_choices</t>
+          <t>rating_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'satisfactory'}</t>
+          <t>satisfactory</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Satisfactory'}</t>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>employee_rating_choices</t>
+          <t>rating_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'needs_improvement'}</t>
+          <t>needs_improvement</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Needs Improvement'}</t>
+          <t>Needs Improvement</t>
         </is>
       </c>
     </row>
@@ -1182,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1199,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1216,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1233,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'increased'}</t>
+          <t>increased</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Increased'}</t>
+          <t>Increased</t>
         </is>
       </c>
     </row>
@@ -1250,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'decreased'}</t>
+          <t>decreased</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Decreased'}</t>
+          <t>Decreased</t>
         </is>
       </c>
     </row>
@@ -1267,63 +1014,63 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'no_change'}</t>
+          <t>no_change</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'No Change'}</t>
+          <t>No Change</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rating_2_choices</t>
+          <t>employee_progress_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'excellent'}</t>
+          <t>increased</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Excellent'}</t>
+          <t>Increased</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rating_2_choices</t>
+          <t>employee_progress_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'satisfactory'}</t>
+          <t>decreased</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Satisfactory'}</t>
+          <t>Decreased</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rating_2_choices</t>
+          <t>employee_progress_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'needs_improvement'}</t>
+          <t>no_change</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Needs Improvement'}</t>
+          <t>No Change</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1369,63 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not Applicable'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>employee_progress_2_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'increased'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Increased'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>employee_progress_2_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'decreased'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Decreased'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>employee_progress_2_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'no_change'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'No Change'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
